--- a/PCB FILES/AV-GMK MK I.xlsx
+++ b/PCB FILES/AV-GMK MK I.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avest\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avest\Desktop\GMK\AV-GMK-MKI\PCB FILES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17482EE0-E18D-4E51-B006-17DC04BF7777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F16404A-25F2-4E04-8987-0ECB3A7AF85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22455" yWindow="1380" windowWidth="21600" windowHeight="11385" xr2:uid="{1C92DB2F-6081-4DBC-A027-5EE29CBB0076}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{1C92DB2F-6081-4DBC-A027-5EE29CBB0076}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>where to get the shit</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>total cost</t>
-  </si>
-  <si>
-    <t>idk yet</t>
   </si>
   <si>
     <t>filament</t>
@@ -88,7 +85,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -145,12 +142,12 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -172,7 +169,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="172" formatCode="#,##0.00\ &quot;€&quot;"/>
+      <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
     </dxf>
     <dxf>
       <font>
@@ -230,10 +227,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE85F295-4C23-47E5-BA29-D1AB73F42C39}" name="Tableau1" displayName="Tableau1" ref="A1:B13" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FE85F295-4C23-47E5-BA29-D1AB73F42C39}" name="Tableau1" displayName="Tableau1" ref="A1:B13" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
   <autoFilter ref="A1:B13" xr:uid="{FE85F295-4C23-47E5-BA29-D1AB73F42C39}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{02E78895-C356-4EC8-BD8D-0390D54EEFE5}" name="where to get the shit" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{02E78895-C356-4EC8-BD8D-0390D54EEFE5}" name="where to get the shit" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{0686B0E8-FDA2-4D5D-8B0C-7DCAFA337A62}" name="cost" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -241,9 +238,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -281,7 +278,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -387,7 +384,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -529,7 +526,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -613,8 +610,8 @@
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
+      <c r="B9" s="2">
+        <v>235.02</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
@@ -643,7 +640,7 @@
     </row>
     <row r="13" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>22.79</v>
@@ -658,7 +655,7 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B2:B13)</f>
-        <v>305.68</v>
+        <v>540.69999999999993</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
